--- a/artfynd/A 11973-2026 artfynd.xlsx
+++ b/artfynd/A 11973-2026 artfynd.xlsx
@@ -675,45 +675,35 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124078095</v>
+        <v>124078018</v>
       </c>
       <c r="B2" t="n">
-        <v>57529</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
@@ -756,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Synligt i en radie av ca 50 meter.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124078165</v>
+        <v>124078095</v>
       </c>
       <c r="B3" t="n">
-        <v>8447</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,24 +788,29 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
@@ -884,37 +879,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124078018</v>
+        <v>124078165</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -960,11 +950,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Synligt i en radie av ca 50 meter.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -994,12 +979,7 @@
         <v>124077929</v>
       </c>
       <c r="B5" t="n">
-        <v>78547</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 11973-2026 artfynd.xlsx
+++ b/artfynd/A 11973-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124078018</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124078095</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124078165</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1070,8 +1090,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124077929</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>